--- a/inputs/metadata.xlsx
+++ b/inputs/metadata.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,67 +421,367 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>样例文档一.pdf</v>
+        <v>浅析固体废物污染防治及管理.pdf</v>
       </c>
       <c r="B2" t="str">
-        <v>生活垃圾分类投放指引（样例一）</v>
+        <v>浅析固体废物污染防治及管理</v>
       </c>
       <c r="C2" t="str">
-        <v>示例公益基金会</v>
-      </c>
-      <c r="D2">
-        <v>2023</v>
+        <v>生态环境与保护</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2019</v>
       </c>
       <c r="E2" t="str">
-        <v>投放指引</v>
+        <v>测试资料</v>
       </c>
       <c r="F2" t="str">
-        <v>垃圾分类、塑料</v>
+        <v>固体废物、污染防治</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>样例文档二.pdf</v>
+        <v>浅析固体废物污染防治与管理.pdf</v>
       </c>
       <c r="B3" t="str">
-        <v>塑料制品减量与回收指南（样例二）</v>
+        <v>浅析固体废物污染防治与管理</v>
       </c>
       <c r="C3" t="str">
-        <v>示例公益基金会</v>
-      </c>
-      <c r="D3">
-        <v>2024</v>
+        <v>生态环境与保护</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2020</v>
       </c>
       <c r="E3" t="str">
-        <v>操作指南</v>
+        <v>测试资料</v>
       </c>
       <c r="F3" t="str">
-        <v>垃圾分类、塑料</v>
+        <v>固体废物、污染防治</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>样例文档三.pdf</v>
+        <v>环境工程建设中固体废物治理.pdf</v>
       </c>
       <c r="B4" t="str">
-        <v>厨余垃圾处理流程（样例三）</v>
+        <v>环境工程建设中固体废物治理</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>地质研究与环境保护</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>2025</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>测试资料</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>固体废物、环境工程</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>环境工程中垃圾处理利用的探究.pdf</v>
+      </c>
+      <c r="B5" t="str">
+        <v>环境工程中垃圾处理利用的探究</v>
+      </c>
+      <c r="C5" t="str">
+        <v>生态环境与保护</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2020</v>
+      </c>
+      <c r="E5" t="str">
+        <v>测试资料</v>
+      </c>
+      <c r="F5" t="str">
+        <v>环境工程</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>浅谈环境工程中固体废物的治理.pdf</v>
+      </c>
+      <c r="B6" t="str">
+        <v>浅谈环境工程中固体废物的治理</v>
+      </c>
+      <c r="C6" t="str">
+        <v>智能城市应用</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2021</v>
+      </c>
+      <c r="E6" t="str">
+        <v>测试资料</v>
+      </c>
+      <c r="F6" t="str">
+        <v>固体废物、环境工程</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>浅析垃圾填埋场环境污染风险及防控.pdf</v>
+      </c>
+      <c r="B7" t="str">
+        <v>浅析垃圾填埋场环境污染风险及防控</v>
+      </c>
+      <c r="C7" t="str">
+        <v>工程学研究与实用</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2022</v>
+      </c>
+      <c r="E7" t="str">
+        <v>测试资料</v>
+      </c>
+      <c r="F7" t="str">
+        <v>填埋处置、污染防治</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>浅谈固体废物的污染防治与管理对策.pdf</v>
+      </c>
+      <c r="B8" t="str">
+        <v>浅谈固体废物的污染防治与管理对策</v>
+      </c>
+      <c r="C8" t="str">
+        <v>地质研究与环境保护</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2023</v>
+      </c>
+      <c r="E8" t="str">
+        <v>测试资料</v>
+      </c>
+      <c r="F8" t="str">
+        <v>固体废物、污染防治</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>浅谈生活垃圾焚烧发电厂环境保护管理.pdf</v>
+      </c>
+      <c r="B9" t="str">
+        <v>浅谈生活垃圾焚烧发电厂环境保护管理</v>
+      </c>
+      <c r="C9" t="str">
+        <v>地质研究与环境保护</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2023</v>
+      </c>
+      <c r="E9" t="str">
+        <v>测试资料</v>
+      </c>
+      <c r="F9" t="str">
+        <v>焚烧处置、污染防治</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>工业固体废物现状及环境保护防治方法分析.pdf</v>
+      </c>
+      <c r="B10" t="str">
+        <v>工业固体废物现状及环境保护防治方法分析</v>
+      </c>
+      <c r="C10" t="str">
+        <v>生态环境与保护</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2020</v>
+      </c>
+      <c r="E10" t="str">
+        <v>测试资料</v>
+      </c>
+      <c r="F10" t="str">
+        <v>固体废物、污染防治</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>循环经济模式下生态环境保护的实践与反思.pdf</v>
+      </c>
+      <c r="B11" t="str">
+        <v>循环经济模式下生态环境保护的实践与反思</v>
+      </c>
+      <c r="C11" t="str">
+        <v>地质研究与环境保护</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E11" t="str">
+        <v>测试资料</v>
+      </c>
+      <c r="F11" t="str">
+        <v>循环经济、污染防治</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>固体废弃物资源化利用中的环境工程技术创新.pdf</v>
+      </c>
+      <c r="B12" t="str">
+        <v>固体废弃物资源化利用中的环境工程技术创新</v>
+      </c>
+      <c r="C12" t="str">
+        <v>工程学研究与实用</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E12" t="str">
+        <v>测试资料</v>
+      </c>
+      <c r="F12" t="str">
+        <v>资源化利用、固体废物、环境工程</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>农业废弃物资源化利用与环境污染综合治理五位一体生态循环.pdf</v>
+      </c>
+      <c r="B13" t="str">
+        <v>农业废弃物资源化利用与环境污染综合治理五位一体生态循环</v>
+      </c>
+      <c r="C13" t="str">
+        <v>生态环境与保护</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2020</v>
+      </c>
+      <c r="E13" t="str">
+        <v>测试资料</v>
+      </c>
+      <c r="F13" t="str">
+        <v>农业废弃物、资源化利用、循环经济</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>生态环境工程咨询在城市固体废弃物处理与资源化利用中的探讨.pdf</v>
+      </c>
+      <c r="B14" t="str">
+        <v>生态环境工程咨询在城市固体废弃物处理与资源化利用中的探讨</v>
+      </c>
+      <c r="C14" t="str">
+        <v>地质研究与环境保护</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E14" t="str">
+        <v>测试资料</v>
+      </c>
+      <c r="F14" t="str">
+        <v>资源化利用、固体废物、环境工程</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>农村垃圾分类现状分析.pdf</v>
+      </c>
+      <c r="B15" t="str">
+        <v>农村垃圾分类现状分析</v>
+      </c>
+      <c r="C15" t="str">
+        <v>城市建筑与发展</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E15" t="str">
+        <v>测试资料</v>
+      </c>
+      <c r="F15" t="str">
+        <v>垃圾分类、农村治理</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>垃圾填埋场稳定性分析.pdf</v>
+      </c>
+      <c r="B16" t="str">
+        <v>垃圾填埋场稳定性分析</v>
+      </c>
+      <c r="C16" t="str">
+        <v>工程管理与技术探讨</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E16" t="str">
+        <v>测试资料</v>
+      </c>
+      <c r="F16" t="str">
+        <v>填埋处置</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>危险废物处理现状研究.pdf</v>
+      </c>
+      <c r="B17" t="str">
+        <v>危险废物处理现状研究</v>
+      </c>
+      <c r="C17" t="str">
+        <v>地质研究与环境保护</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2023</v>
+      </c>
+      <c r="E17" t="str">
+        <v>测试资料</v>
+      </c>
+      <c r="F17" t="str">
+        <v>危险废物</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>园林废弃物的资源化利用.pdf</v>
+      </c>
+      <c r="B18" t="str">
+        <v>园林废弃物的资源化利用</v>
+      </c>
+      <c r="C18" t="str">
+        <v>工程管理与技术探讨</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2025</v>
+      </c>
+      <c r="E18" t="str">
+        <v>测试资料</v>
+      </c>
+      <c r="F18" t="str">
+        <v>园林废弃物、资源化利用</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>农村生活垃圾分类治理探讨.pdf</v>
+      </c>
+      <c r="B19" t="str">
+        <v>农村生活垃圾分类治理探讨</v>
+      </c>
+      <c r="C19" t="str">
+        <v>地质研究与环境保护</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2022</v>
+      </c>
+      <c r="E19" t="str">
+        <v>测试资料</v>
+      </c>
+      <c r="F19" t="str">
+        <v>垃圾分类、农村治理</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F19"/>
   </ignoredErrors>
 </worksheet>
 </file>